--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488079_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488079_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7883</v>
+        <v>4.4153</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1838</v>
+        <v>3.6142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6045</v>
+        <v>0.8011</v>
       </c>
       <c r="G2" t="n">
         <v>4.6938</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1721</v>
+        <v>-0.5451</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4241</v>
+        <v>-0.9937</v>
       </c>
       <c r="U2" t="n">
-        <v>0.252</v>
+        <v>0.4486</v>
       </c>
       <c r="V2" t="n">
         <v>0.2666</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.287</v>
+        <v>3.3607</v>
       </c>
       <c r="E3" t="n">
-        <v>3.093</v>
+        <v>3.1949</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1939</v>
+        <v>0.1659</v>
       </c>
       <c r="G3" t="n">
         <v>5.3966</v>
@@ -688,13 +688,13 @@
         <v>0.3964</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9292</v>
+        <v>-0.8554</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.624</v>
+        <v>-0.5221</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3052</v>
+        <v>-0.3333</v>
       </c>
       <c r="V3" t="n">
         <v>0.6036</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5156</v>
+        <v>3.0521</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6969</v>
+        <v>1.065</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8187</v>
+        <v>1.9872</v>
       </c>
       <c r="G4" t="n">
         <v>2.495</v>
@@ -766,13 +766,13 @@
         <v>1.9822</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9705</v>
+        <v>-0.434</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1232</v>
+        <v>-0.7551</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1526</v>
+        <v>0.3211</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>P. LÓPEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2157</v>
+        <v>1.2053</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7466</v>
+        <v>1.2053</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4691</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.059</v>
+        <v>1.2053</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0271</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0861</v>
+        <v>1.2053</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1812</v>
+        <v>1.2053</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1009</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0804</v>
+        <v>1.2053</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1223</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.128</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5654</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1949</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. LÓPEZ GÓMEZ</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2053</v>
+        <v>1.0005</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2053</v>
+        <v>0.5034</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.4971</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2053</v>
+        <v>0.059</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.0271</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2053</v>
+        <v>0.0861</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2053</v>
+        <v>0.1812</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.1009</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2053</v>
+        <v>0.0804</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.1223</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.128</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.5451</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.3222</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.2804</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.414</v>
+        <v>-1.0386</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4908</v>
+        <v>1.319</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8784</v>
+        <v>-0.1412</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8592</v>
+        <v>0.1383</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0192</v>
+        <v>-0.2794</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1772</v>
+        <v>-0.3234</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7391</v>
+        <v>0.1147</v>
       </c>
       <c r="L8" t="n">
         <v>-0.4381</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2988</v>
+        <v>0.1822</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1201</v>
+        <v>0.0235</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4189</v>
+        <v>0.1586</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.1982</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6196</v>
+        <v>-1.2325</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6312</v>
+        <v>-0.7836</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0116</v>
+        <v>-0.4489</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4074</v>
+        <v>0.2666</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.4074</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2254</v>
+        <v>0.1707</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7834</v>
+        <v>-2.4154</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5581</v>
+        <v>2.5861</v>
       </c>
       <c r="G9" t="n">
         <v>1.115</v>
@@ -1156,13 +1156,13 @@
         <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3909</v>
+        <v>-0.9948</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1232</v>
+        <v>-0.7551</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2678</v>
+        <v>-0.2397</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9405</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2649</v>
+        <v>-0.005</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3562</v>
+        <v>-0.1525</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1475</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2531</v>
@@ -1234,13 +1234,13 @@
         <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3993</v>
+        <v>-0.1394</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4368</v>
+        <v>-0.233</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6036</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3008</v>
+        <v>-0.391</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3671</v>
+        <v>-2.6572</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0663</v>
+        <v>2.2662</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1412</v>
+        <v>-0.8784</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1383</v>
+        <v>-0.8592</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2794</v>
+        <v>-0.0192</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3234</v>
+        <v>-1.1772</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1147</v>
+        <v>-0.7391</v>
       </c>
       <c r="L11" t="n">
         <v>-0.4381</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1822</v>
+        <v>0.2988</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0235</v>
+        <v>-0.1201</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1586</v>
+        <v>0.4189</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.1982</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8138</v>
+        <v>-1.0875</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1121</v>
+        <v>-0.8744</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7016</v>
+        <v>-0.213</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2666</v>
+        <v>-0.4074</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2666</v>
+        <v>-0.4074</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6581</v>
+        <v>-0.8451</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5079</v>
+        <v>-1.7511</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8498</v>
+        <v>0.906</v>
       </c>
       <c r="G12" t="n">
         <v>0.1084</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5683</v>
+        <v>-0.7553</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1834</v>
+        <v>-0.4266</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3849</v>
+        <v>-0.3287</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7911</v>
+        <v>-1.5397</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1879</v>
+        <v>-0.4311</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6032</v>
+        <v>-1.1086</v>
       </c>
       <c r="G13" t="n">
         <v>-2.4657</v>
@@ -1468,13 +1468,13 @@
         <v>0.7929</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8817</v>
+        <v>0.1331</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2458</v>
+        <v>-0.489</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1275</v>
+        <v>0.6221</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.2698</v>
+        <v>-2.5016</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2566</v>
+        <v>-1.4604</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0132</v>
+        <v>-1.0413</v>
       </c>
       <c r="G14" t="n">
         <v>0.4641</v>
@@ -1546,13 +1546,13 @@
         <v>1.3876</v>
       </c>
       <c r="S14" t="n">
-        <v>0.275</v>
+        <v>0.0432</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1944</v>
+        <v>-0.3982</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4694</v>
+        <v>0.4413</v>
       </c>
       <c r="V14" t="n">
         <v>-2.4142</v>
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.8813</v>
+        <v>8.5053</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6448</v>
+        <v>-0.02080000000000015</v>
       </c>
       <c r="F15" t="n">
-        <v>8.526100000000001</v>
+        <v>8.526199999999999</v>
       </c>
       <c r="G15" t="n">
         <v>12.1015</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6989000000000003</v>
+        <v>0.6988999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>11.4027</v>
@@ -1603,7 +1603,7 @@
         <v>4.9267</v>
       </c>
       <c r="L15" t="n">
-        <v>8.543600000000001</v>
+        <v>8.543600000000003</v>
       </c>
       <c r="M15" t="n">
         <v>-1.3689</v>
@@ -1624,13 +1624,13 @@
         <v>14.8667</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.946800000000001</v>
+        <v>-5.322600000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-6.532799999999999</v>
+        <v>-5.9086</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5858999999999999</v>
+        <v>0.5861000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-3.2289</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.708</v>
+        <v>3.4269</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1663</v>
+        <v>1.7775</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5417</v>
+        <v>1.6494</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1947</v>
@@ -1702,13 +1702,13 @@
         <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3748</v>
+        <v>0.3441</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3617</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9869</v>
+        <v>1.0946</v>
       </c>
       <c r="V16" t="n">
         <v>2.4846</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>F. MALENO BERENGUER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5899</v>
+        <v>0.9175</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1502</v>
+        <v>1.3444</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4397</v>
+        <v>-0.4269</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9506</v>
+        <v>0.3845</v>
       </c>
       <c r="H17" t="n">
-        <v>3.663</v>
+        <v>1.1727</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7123</v>
+        <v>-0.7883</v>
       </c>
       <c r="J17" t="n">
-        <v>3.121</v>
+        <v>1.033</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3186</v>
+        <v>1.0291</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1975</v>
+        <v>0.0039</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1704</v>
+        <v>-0.6485</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6556</v>
+        <v>0.1437</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5148</v>
+        <v>-0.7922</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.7751</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1627</v>
+        <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1478</v>
+        <v>0.3854</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9253</v>
+        <v>0.0955</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2225</v>
+        <v>0.2899</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2666</v>
+        <v>0.9405</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. YELAMOS MAÑAS</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3027</v>
+        <v>0.6581</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3027</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.3228</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3027</v>
+        <v>1.9506</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3027</v>
+        <v>3.663</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-1.7123</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3027</v>
+        <v>3.121</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3027</v>
+        <v>4.3186</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.1975</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.1704</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.6556</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.5148</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.1627</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.216</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1103</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.1057</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. MALENO BERENGUER</t>
+          <t>J. YELAMOS MAÑAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1731</v>
+        <v>0.3027</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.3027</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7638</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3845</v>
+        <v>0.3027</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1727</v>
+        <v>0.3027</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7883</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.033</v>
+        <v>0.3027</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0291</v>
+        <v>0.3027</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0039</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6485</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1437</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7922</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.359</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.312</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.047</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9405</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0459</v>
+        <v>0.2882</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2143</v>
+        <v>-0.1124</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2602</v>
+        <v>0.4006</v>
       </c>
       <c r="G20" t="n">
         <v>-1.243</v>
@@ -2014,13 +2014,13 @@
         <v>0.3964</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6259</v>
+        <v>0.8681</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1176</v>
+        <v>0.2194</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5083</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0.2666</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. YELAMOS MANAS</t>
+          <t>G. CARRAL ESCUDERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7216</v>
+        <v>-2.4734</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8244</v>
+        <v>-3.8585</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8973</v>
+        <v>1.3851</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8861</v>
+        <v>-1.3459</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1752</v>
+        <v>-0.2593</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7108</v>
+        <v>-1.0866</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2483</v>
+        <v>0.828</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6122</v>
+        <v>0.3303</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8606</v>
+        <v>0.4977</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6377</v>
+        <v>-2.1739</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7875</v>
+        <v>-0.5896</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8503</v>
+        <v>-1.5843</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7929</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1893</v>
+        <v>-4.1627</v>
       </c>
       <c r="R21" t="n">
         <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4488</v>
+        <v>0.379</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6133</v>
+        <v>-0.5238</v>
       </c>
       <c r="U21" t="n">
-        <v>1.8355</v>
+        <v>0.9029</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0772</v>
+        <v>0.674</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0772</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ VILLEGAS</t>
+          <t>J. YELAMOS MANAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4599</v>
+        <v>-2.7305</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2874</v>
+        <v>-1.4356</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1725</v>
+        <v>-1.2949</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0383</v>
+        <v>-2.8861</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2604</v>
+        <v>-0.1752</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.778</v>
+        <v>-2.7108</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6473</v>
+        <v>-0.2483</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3292</v>
+        <v>0.6122</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3181</v>
+        <v>-0.8606</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.391</v>
+        <v>-2.6377</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9312</v>
+        <v>-0.7875</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4599</v>
+        <v>-1.8503</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7929</v>
+        <v>0.7929</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1982</v>
+        <v>1.9822</v>
       </c>
       <c r="S22" t="n">
-        <v>1.9045</v>
+        <v>1.4399</v>
       </c>
       <c r="T22" t="n">
-        <v>1.351</v>
+        <v>0.0021</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5534</v>
+        <v>1.4378</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5331</v>
+        <v>-2.0772</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5331</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. CARRAL ESCUDERO</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6592</v>
+        <v>-3.4644</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5716</v>
+        <v>-3.9809</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9124</v>
+        <v>0.5165</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3459</v>
+        <v>-5.0312</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2593</v>
+        <v>-3.8622</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0866</v>
+        <v>-1.169</v>
       </c>
       <c r="J23" t="n">
-        <v>0.828</v>
+        <v>-2.7953</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3303</v>
+        <v>-2.803</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4977</v>
+        <v>0.0078</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1739</v>
+        <v>-2.236</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5896</v>
+        <v>-1.0591</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5843</v>
+        <v>-1.1768</v>
       </c>
       <c r="P23" t="n">
+        <v>-0.3964</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-2.1805</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-4.1627</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8068</v>
+        <v>0.7562</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2369</v>
+        <v>-0.4788</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4301</v>
+        <v>1.235</v>
       </c>
       <c r="V23" t="n">
-        <v>0.674</v>
+        <v>1.2071</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X23" t="n">
-        <v>0.674</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>A. RODRIGUEZ VILLEGAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8601</v>
+        <v>-4.1273</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1846</v>
+        <v>-1.8986</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3245</v>
+        <v>-2.2287</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.0312</v>
+        <v>-4.0383</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.8622</v>
+        <v>-1.2604</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.169</v>
+        <v>-2.778</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.7953</v>
+        <v>-1.6473</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.803</v>
+        <v>-0.3292</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0078</v>
+        <v>-1.3181</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.236</v>
+        <v>-2.391</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0591</v>
+        <v>-0.9312</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1768</v>
+        <v>-1.4599</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R24" t="n">
-        <v>1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3605</v>
+        <v>1.2371</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6826</v>
+        <v>0.7398</v>
       </c>
       <c r="U24" t="n">
-        <v>1.043</v>
+        <v>0.4973</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2071</v>
+        <v>-0.5331</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2666</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="25">
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.881199999999999</v>
+        <v>-7.2022</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.5261</v>
+        <v>-8.526199999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6449</v>
+        <v>1.3239</v>
       </c>
       <c r="G25" t="n">
         <v>-12.1014</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6987999999999999</v>
+        <v>-0.6987999999999996</v>
       </c>
       <c r="I25" t="n">
         <v>-11.4026</v>
       </c>
       <c r="J25" t="n">
-        <v>1.368900000000001</v>
+        <v>1.3689</v>
       </c>
       <c r="K25" t="n">
         <v>4.228</v>
@@ -2392,7 +2392,7 @@
         <v>-4.9267</v>
       </c>
       <c r="O25" t="n">
-        <v>-8.543700000000001</v>
+        <v>-8.543699999999999</v>
       </c>
       <c r="P25" t="n">
         <v>-4.9556</v>
@@ -2404,13 +2404,13 @@
         <v>9.911</v>
       </c>
       <c r="S25" t="n">
-        <v>5.946899999999999</v>
+        <v>6.6258</v>
       </c>
       <c r="T25" t="n">
         <v>-0.5860000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>6.5327</v>
+        <v>7.2119</v>
       </c>
       <c r="V25" t="n">
         <v>3.2291</v>
